--- a/Curs Oficial/sesiuni/s05/echipa_verde/Magazine.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_verde/Magazine.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Magazine" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magazine" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,14 +422,6 @@
           <t>Farmacii</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -437,14 +429,6 @@
           <t>Coordonate WGS84 — verificati semnul</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
